--- a/docs/downloads/05/tbl_agri_equip_alaotra_ambatomanga.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_ambatomanga.xlsx
@@ -436,12 +436,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +448,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -472,12 +460,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -490,12 +472,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -508,12 +484,6 @@
           <t>Charrue</t>
         </is>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -580,12 +550,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -598,12 +562,6 @@
           <t>Herse/Pulvériseur/Rotovat</t>
         </is>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -616,12 +574,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +586,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -670,12 +616,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -706,12 +646,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +658,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,12 +670,6 @@
           <t>Soubique, produits de tis</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +682,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -827,12 +743,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -845,12 +755,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -863,12 +767,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -899,12 +797,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -935,12 +827,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -953,12 +839,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -971,12 +851,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1025,12 +899,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C38">
-        <v>3</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1223,12 +1091,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1277,12 +1139,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C52">
-        <v>4</v>
-      </c>
-      <c r="D52">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1295,12 +1151,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C53">
-        <v>3</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1312,12 +1162,6 @@
         <is>
           <t>Soubique, produits de tis</t>
         </is>
-      </c>
-      <c r="C54">
-        <v>2</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
